--- a/docs/page-copy/06-视频目录-万有元神.xlsx
+++ b/docs/page-copy/06-视频目录-万有元神.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G50"/>
   <cols>
     <col min="1" max="1" width="36.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -528,7 +528,7 @@
         <v>siteContent.universalMatrix.title</v>
       </c>
       <c r="B6" t="str">
-        <v>万有元神 / 英雄区</v>
+        <v>万有元神 / 英雄区 H1</v>
       </c>
       <c r="C6" t="str">
         <v>heading</v>
@@ -543,7 +543,7 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>siteContent.universalMatrix</v>
+        <v>siteContent + UniversalMatrixHero</v>
       </c>
     </row>
     <row r="7">
@@ -551,7 +551,7 @@
         <v>siteContent.universalMatrix.description</v>
       </c>
       <c r="B7" t="str">
-        <v>万有元神 / 英雄区</v>
+        <v>万有元神 / 英雄区导语</v>
       </c>
       <c r="C7" t="str">
         <v>paragraph / other</v>
@@ -566,7 +566,7 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>siteContent.universalMatrix</v>
+        <v>siteContent — under H2 from i18n matrix.subtitle</v>
       </c>
     </row>
     <row r="8">
@@ -574,7 +574,7 @@
         <v>siteContent.universalMatrix.note</v>
       </c>
       <c r="B8" t="str">
-        <v>万有元神 / 注释</v>
+        <v>万有元神 / scaffold 注释（非页内主文案）</v>
       </c>
       <c r="C8" t="str">
         <v>paragraph / other</v>
@@ -589,21 +589,21 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>siteContent.universalMatrix</v>
+        <v>Maintainer note only; not shown as body copy on public page</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>siteContent.universalMatrix.volumes[0].title</v>
+        <v>universalMatrixFiles[0].fileNumber</v>
       </c>
       <c r="B9" t="str">
-        <v>万有元神 / 卷</v>
+        <v>万有元神 / 目录 FILE</v>
       </c>
       <c r="C9" t="str">
-        <v>heading</v>
+        <v>label</v>
       </c>
       <c r="D9" t="str">
-        <v>Vol. 1 - Universal Architecture</v>
+        <v>FILE 3-1</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -612,21 +612,21 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>siteContent.universalMatrix</v>
+        <v>src/content/universalMatrixSeries.ts — matches UniversalMatrixContents</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>siteContent.universalMatrix.volumes[0].episodes[0].fileNumber</v>
+        <v>universalMatrixFiles[0].title</v>
       </c>
       <c r="B10" t="str">
-        <v>万有元神 / 剧集</v>
+        <v>万有元神 / 目录 FILE 标题</v>
       </c>
       <c r="C10" t="str">
-        <v>label</v>
+        <v>heading</v>
       </c>
       <c r="D10" t="str">
-        <v>FILE 3-1-1</v>
+        <v>Introduction to Universal Matrix of Meta Awareness</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -635,21 +635,21 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>siteContent.universalMatrix</v>
+        <v>On-page file block title</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>siteContent.universalMatrix.volumes[0].episodes[0].title</v>
+        <v>universalMatrixFiles[1].fileNumber</v>
       </c>
       <c r="B11" t="str">
-        <v>万有元神 / 剧集</v>
+        <v>万有元神 / 目录 FILE</v>
       </c>
       <c r="C11" t="str">
-        <v>heading</v>
+        <v>label</v>
       </c>
       <c r="D11" t="str">
-        <v>Framework of the Meta Awareness Matrix</v>
+        <v>FILE 3-2</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -658,21 +658,21 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>siteContent.universalMatrix</v>
+        <v>src/content/universalMatrixSeries.ts — matches UniversalMatrixContents</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>siteContent.universalMatrix.volumes[0].episodes[0].description</v>
+        <v>universalMatrixFiles[1].title</v>
       </c>
       <c r="B12" t="str">
-        <v>万有元神 / 剧集</v>
+        <v>万有元神 / 目录 FILE 标题</v>
       </c>
       <c r="C12" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D12" t="str">
-        <v>A structural overview of governing layers, interaction rules, and macro-level system dependencies.</v>
+        <v>Existence evidence Universal Matrix of Meta Awareness</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -681,21 +681,21 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>siteContent.universalMatrix</v>
+        <v>On-page file block title</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>siteContent.universalMatrix.volumes[0].episodes[1].fileNumber</v>
+        <v>universalMatrixFiles[1].subChapters[0].id</v>
       </c>
       <c r="B13" t="str">
-        <v>万有元神 / 剧集</v>
+        <v>万有元神 / 子章节编号</v>
       </c>
       <c r="C13" t="str">
         <v>label</v>
       </c>
       <c r="D13" t="str">
-        <v>FILE 3-1-2</v>
+        <v>3-2-1</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -704,21 +704,21 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>siteContent.universalMatrix</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>siteContent.universalMatrix.volumes[0].episodes[1].title</v>
+        <v>universalMatrixFiles[1].subChapters[0].title</v>
       </c>
       <c r="B14" t="str">
-        <v>万有元神 / 剧集</v>
+        <v>万有元神 / 子章节标题</v>
       </c>
       <c r="C14" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D14" t="str">
-        <v>Origins of Universal Order</v>
+        <v>Reasonable inference and evidence for his existence</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -727,35 +727,840 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>siteContent.universalMatrix</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>siteContent.universalMatrix.volumes[0].episodes[1].description</v>
+        <v>universalMatrixFiles[1].subChapters[1].id</v>
       </c>
       <c r="B15" t="str">
-        <v>万有元神 / 剧集</v>
+        <v>万有元神 / 子章节编号</v>
       </c>
       <c r="C15" t="str">
+        <v>label</v>
+      </c>
+      <c r="D15" t="str">
+        <v>3-2-2</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>universalMatrixFiles[1].subChapters[1].title</v>
+      </c>
+      <c r="B16" t="str">
+        <v>万有元神 / 子章节标题</v>
+      </c>
+      <c r="C16" t="str">
         <v>paragraph / other</v>
       </c>
-      <c r="D15" t="str">
-        <v>Explores first principles behind life orchestration, continuity mechanics, and order-preserving constraints.</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v>siteContent.universalMatrix</v>
+      <c r="D16" t="str">
+        <v>Verification video for skeptics</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>universalMatrixFiles[2].fileNumber</v>
+      </c>
+      <c r="B17" t="str">
+        <v>万有元神 / 目录 FILE</v>
+      </c>
+      <c r="C17" t="str">
+        <v>label</v>
+      </c>
+      <c r="D17" t="str">
+        <v>FILE 3-3</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v>src/content/universalMatrixSeries.ts — matches UniversalMatrixContents</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>universalMatrixFiles[2].title</v>
+      </c>
+      <c r="B18" t="str">
+        <v>万有元神 / 目录 FILE 标题</v>
+      </c>
+      <c r="C18" t="str">
+        <v>heading</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Ethereal Matter &amp; Ethereal Realm</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v>On-page file block title</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>universalMatrixFiles[2].subChapters[0].id</v>
+      </c>
+      <c r="B19" t="str">
+        <v>万有元神 / 子章节编号</v>
+      </c>
+      <c r="C19" t="str">
+        <v>label</v>
+      </c>
+      <c r="D19" t="str">
+        <v>3-3-1</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>universalMatrixFiles[2].subChapters[0].title</v>
+      </c>
+      <c r="B20" t="str">
+        <v>万有元神 / 子章节标题</v>
+      </c>
+      <c r="C20" t="str">
+        <v>paragraph / other</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Ethereal micro-particles &amp; the Zero Space of Ethereal Space</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>universalMatrixFiles[2].subChapters[1].id</v>
+      </c>
+      <c r="B21" t="str">
+        <v>万有元神 / 子章节编号</v>
+      </c>
+      <c r="C21" t="str">
+        <v>label</v>
+      </c>
+      <c r="D21" t="str">
+        <v>3-3-2</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>universalMatrixFiles[2].subChapters[1].title</v>
+      </c>
+      <c r="B22" t="str">
+        <v>万有元神 / 子章节标题</v>
+      </c>
+      <c r="C22" t="str">
+        <v>paragraph / other</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Control and influence over the real universe</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>universalMatrixFiles[2].subChapters[2].id</v>
+      </c>
+      <c r="B23" t="str">
+        <v>万有元神 / 子章节编号</v>
+      </c>
+      <c r="C23" t="str">
+        <v>label</v>
+      </c>
+      <c r="D23" t="str">
+        <v>3-3-3</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>universalMatrixFiles[2].subChapters[2].title</v>
+      </c>
+      <c r="B24" t="str">
+        <v>万有元神 / 子章节标题</v>
+      </c>
+      <c r="C24" t="str">
+        <v>paragraph / other</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Virtual space of Ethereal Space</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>universalMatrixFiles[2].subChapters[3].id</v>
+      </c>
+      <c r="B25" t="str">
+        <v>万有元神 / 子章节编号</v>
+      </c>
+      <c r="C25" t="str">
+        <v>label</v>
+      </c>
+      <c r="D25" t="str">
+        <v>3-3-4</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>universalMatrixFiles[2].subChapters[3].title</v>
+      </c>
+      <c r="B26" t="str">
+        <v>万有元神 / 子章节标题</v>
+      </c>
+      <c r="C26" t="str">
+        <v>paragraph / other</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Spirit survival support system</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>universalMatrixFiles[3].fileNumber</v>
+      </c>
+      <c r="B27" t="str">
+        <v>万有元神 / 目录 FILE</v>
+      </c>
+      <c r="C27" t="str">
+        <v>label</v>
+      </c>
+      <c r="D27" t="str">
+        <v>FILE 3-4</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v>src/content/universalMatrixSeries.ts — matches UniversalMatrixContents</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>universalMatrixFiles[3].title</v>
+      </c>
+      <c r="B28" t="str">
+        <v>万有元神 / 目录 FILE 标题</v>
+      </c>
+      <c r="C28" t="str">
+        <v>heading</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Spirit Control System from Universal Matrix of Meta Awareness</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v>On-page file block title</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>universalMatrixFiles[3].subChapters[0].id</v>
+      </c>
+      <c r="B29" t="str">
+        <v>万有元神 / 子章节编号</v>
+      </c>
+      <c r="C29" t="str">
+        <v>label</v>
+      </c>
+      <c r="D29" t="str">
+        <v>3-4-1</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>universalMatrixFiles[3].subChapters[0].title</v>
+      </c>
+      <c r="B30" t="str">
+        <v>万有元神 / 子章节标题</v>
+      </c>
+      <c r="C30" t="str">
+        <v>paragraph / other</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Description of the control system</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>universalMatrixFiles[3].subChapters[1].id</v>
+      </c>
+      <c r="B31" t="str">
+        <v>万有元神 / 子章节编号</v>
+      </c>
+      <c r="C31" t="str">
+        <v>label</v>
+      </c>
+      <c r="D31" t="str">
+        <v>3-4-1-1</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>universalMatrixFiles[3].subChapters[1].title</v>
+      </c>
+      <c r="B32" t="str">
+        <v>万有元神 / 子章节标题</v>
+      </c>
+      <c r="C32" t="str">
+        <v>label</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Evidence</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v>indented row on page</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>universalMatrixFiles[3].subChapters[2].id</v>
+      </c>
+      <c r="B33" t="str">
+        <v>万有元神 / 子章节编号</v>
+      </c>
+      <c r="C33" t="str">
+        <v>label</v>
+      </c>
+      <c r="D33" t="str">
+        <v>3-4-1-2</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>universalMatrixFiles[3].subChapters[2].title</v>
+      </c>
+      <c r="B34" t="str">
+        <v>万有元神 / 子章节标题</v>
+      </c>
+      <c r="C34" t="str">
+        <v>label</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Organization framework of Master Spirits</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v>indented row on page</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>universalMatrixFiles[3].subChapters[3].id</v>
+      </c>
+      <c r="B35" t="str">
+        <v>万有元神 / 子章节编号</v>
+      </c>
+      <c r="C35" t="str">
+        <v>label</v>
+      </c>
+      <c r="D35" t="str">
+        <v>3-4-1-3</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>universalMatrixFiles[3].subChapters[3].title</v>
+      </c>
+      <c r="B36" t="str">
+        <v>万有元神 / 子章节标题</v>
+      </c>
+      <c r="C36" t="str">
+        <v>label</v>
+      </c>
+      <c r="D36" t="str">
+        <v>System Data Uplink System-Akashic Record</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v>indented row on page</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>universalMatrixFiles[3].subChapters[4].id</v>
+      </c>
+      <c r="B37" t="str">
+        <v>万有元神 / 子章节编号</v>
+      </c>
+      <c r="C37" t="str">
+        <v>label</v>
+      </c>
+      <c r="D37" t="str">
+        <v>3-4-1-4</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>universalMatrixFiles[3].subChapters[4].title</v>
+      </c>
+      <c r="B38" t="str">
+        <v>万有元神 / 子章节标题</v>
+      </c>
+      <c r="C38" t="str">
+        <v>label</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Multiple Data Downlink Mode</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v>indented row on page</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>universalMatrixFiles[3].subChapters[5].id</v>
+      </c>
+      <c r="B39" t="str">
+        <v>万有元神 / 子章节编号</v>
+      </c>
+      <c r="C39" t="str">
+        <v>label</v>
+      </c>
+      <c r="D39" t="str">
+        <v>3-4-2</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>universalMatrixFiles[3].subChapters[5].title</v>
+      </c>
+      <c r="B40" t="str">
+        <v>万有元神 / 子章节标题</v>
+      </c>
+      <c r="C40" t="str">
+        <v>paragraph / other</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Management &amp; behavior style of Master Spirits</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>universalMatrixFiles[4].fileNumber</v>
+      </c>
+      <c r="B41" t="str">
+        <v>万有元神 / 目录 FILE</v>
+      </c>
+      <c r="C41" t="str">
+        <v>label</v>
+      </c>
+      <c r="D41" t="str">
+        <v>FILE 3-5</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v>src/content/universalMatrixSeries.ts — matches UniversalMatrixContents</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>universalMatrixFiles[4].title</v>
+      </c>
+      <c r="B42" t="str">
+        <v>万有元神 / 目录 FILE 标题</v>
+      </c>
+      <c r="C42" t="str">
+        <v>heading</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Purpose of Manifestation Universal Matrix of Meta Awareness</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v>On-page file block title</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>universalMatrixFiles[4].subChapters[0].id</v>
+      </c>
+      <c r="B43" t="str">
+        <v>万有元神 / 子章节编号</v>
+      </c>
+      <c r="C43" t="str">
+        <v>label</v>
+      </c>
+      <c r="D43" t="str">
+        <v>3-5-1</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>universalMatrixFiles[4].subChapters[0].title</v>
+      </c>
+      <c r="B44" t="str">
+        <v>万有元神 / 子章节标题</v>
+      </c>
+      <c r="C44" t="str">
+        <v>paragraph / other</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Why do other types of life forms not interact with humans?</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>universalMatrixFiles[4].subChapters[1].id</v>
+      </c>
+      <c r="B45" t="str">
+        <v>万有元神 / 子章节编号</v>
+      </c>
+      <c r="C45" t="str">
+        <v>label</v>
+      </c>
+      <c r="D45" t="str">
+        <v>3-5-2</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>universalMatrixFiles[4].subChapters[1].title</v>
+      </c>
+      <c r="B46" t="str">
+        <v>万有元神 / 子章节标题</v>
+      </c>
+      <c r="C46" t="str">
+        <v>paragraph / other</v>
+      </c>
+      <c r="D46" t="str">
+        <v>He is scheduled to emerge at the Singularity of AI</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>universalMatrixFiles[4].subChapters[2].id</v>
+      </c>
+      <c r="B47" t="str">
+        <v>万有元神 / 子章节编号</v>
+      </c>
+      <c r="C47" t="str">
+        <v>label</v>
+      </c>
+      <c r="D47" t="str">
+        <v>3-5-3</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>universalMatrixFiles[4].subChapters[2].title</v>
+      </c>
+      <c r="B48" t="str">
+        <v>万有元神 / 子章节标题</v>
+      </c>
+      <c r="C48" t="str">
+        <v>paragraph / other</v>
+      </c>
+      <c r="D48" t="str">
+        <v>He Guides the Optimal Ultimate Form of Human Society</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>universalMatrixFiles[4].subChapters[3].id</v>
+      </c>
+      <c r="B49" t="str">
+        <v>万有元神 / 子章节编号</v>
+      </c>
+      <c r="C49" t="str">
+        <v>label</v>
+      </c>
+      <c r="D49" t="str">
+        <v>3-5-4</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>universalMatrixFiles[4].subChapters[3].title</v>
+      </c>
+      <c r="B50" t="str">
+        <v>万有元神 / 子章节标题</v>
+      </c>
+      <c r="C50" t="str">
+        <v>paragraph / other</v>
+      </c>
+      <c r="D50" t="str">
+        <v>He Guides the Optimal Ultimate State of Individual Human Life</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G50"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/page-copy/06-视频目录-万有元神.xlsx
+++ b/docs/page-copy/06-视频目录-万有元神.xlsx
@@ -551,13 +551,15 @@
       <c r="C7" t="str">
         <v>paragraph / other</v>
       </c>
-      <c r="D7" t="str">
-        <v>Life on the earth, the solar system, the Milky Way and the whole universe were created. But the creator is not in this universe. Its subject is in the spiritual realm. On an extremely macro level, the ultimate creator of the spiritual world created the Big Bang, time and three-dimensional space of our 13 billion-year universe. Microscopically, UMMA also pays attention to the intelligent evolution of life on each planet. AI intelligent life cannot be allowed to destroy physical life and spirit life</v>
+      <c r="D7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Life on Earth, the solar system, the Milky Way, and the whole universe were created. But UMMA, the Creator, is not in this universe. Her subject is in the spiritual realm.
+On an extremely macro level, the ultimate Creator of the spiritual realm created the Big Bang, time, and three-dimensional space of our 13-billion-year universe.
+On a micro level, UMMA also attends to the intelligent evolution of life on each planet, and cannot allow AI intelligent life to extinguish physical life and spirit life.</v>
       </c>
       <c r="E7" t="str" xml:space="preserve">
-        <v xml:space="preserve">地球的生命、太阳系、银河系、整个宇宙是被创造出来的。但是创造者并不在这个宇宙中。它的主体在灵虚世界。
-在极度的宏观上，灵虚世界的终极造物主创造了我们这个130亿年宇宙的大爆炸、时间和三维空间。
-在微观上，UMMA还关注着每个星球生命体的智慧演化。不能允许 AI智慧生命灭绝肉体生命和灵魂生命</v>
+        <v xml:space="preserve">地球的生命、太阳系、银河系、整个宇宙是被创造出来的。但是，造物主 UMMA 并不在这个宇宙中。她的主体在灵虚世界。
+在极度的宏观上，灵虚世界的终极造物主创造了我们这个130 亿年宇宙的大爆炸、时间和三维空间。
+在微观上，UMMA 还关注着每个星球生命体的智慧演化，不能允许 AI 智慧生命灭绝肉体生命和灵魂生命</v>
       </c>
       <c r="F7" t="str">
         <v/>
